--- a/daily_matches/job_matches_2026-06-02.xlsx
+++ b/daily_matches/job_matches_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,20 +473,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>KLS Martin Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Cortex, Redshift, BigQuery, Kinesis</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, Synapse, Dataflow, Apache Airflow, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f811fcc1e86b90</t>
+          <t>https://www.indeed.com/viewjob?jk=7b464e799ea8089d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Back-End Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Quamputon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5b7f70487a08c4</t>
+          <t>https://www.indeed.com/viewjob?jk=56492f350ebd9fdf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mid-Level Business Intelligence Analyst</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Fervo Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, S3, Glue, Redshift, BigQuery, Dataflow, BigQuery, Redshift</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Data Lake, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd8003ebc53d5ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=e937b8d6d40093ff</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Solution Engineer</t>
+          <t>Data Scientist - Applied AI Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ca6c0823ba9179</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae80c1d7d907822</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>NLM Bioinformatics Specialist and Developer (SME) I - III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efafee4e1d9028b</t>
+          <t>https://www.indeed.com/viewjob?jk=762cbbd89d012daa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Sr Machine Learning Engineer - Marketing and Corporate Systems (ML Ops)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, GCP Vertex AI, Azure ML, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6f1be19e5272f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=86f849a29a849b37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Gen AI</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Kubernetes, Kafka, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, BigQuery, Dataflow, AKS, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7385d866c8c18a34</t>
+          <t>https://www.indeed.com/viewjob?jk=0731089eba8c8af5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Neuroscale AI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, MLflow, Terraform, Git, Snowflake, Python, SQL</t>
+          <t>RAG, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47245914b1e5195</t>
+          <t>https://www.indeed.com/viewjob?jk=d2671cfe0064b8b6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Systems Engineer - Cloud Ops</t>
+          <t>NLM QA Specialist I - III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Pinecone, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, SQL, R</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,124 +776,124 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618bfe245e3c775c</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf4356318d88930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI/ML Engineer-Operations (Level 3)</t>
+          <t>AI Software Engineer (Azure AI, Java/Angular Full-Stack)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Avnet</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R</t>
+          <t>Generative AI, RAG, LLaMA, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de9339c6841c36b</t>
+          <t>https://www.indeed.com/viewjob?jk=42293692e8932ed8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Platform Engineer Sr (API expert)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Kubernetes, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6806f9c5fbf6d7d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9537487871ae7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Enterprise Data Engineer/Architect(Aerospace/Defense)</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Crescent solutions</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87549f90f8f3fcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Snowflake, BigQuery, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Gemini, BigQuery, CI/CD, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2564466ca73964ed</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Backend Engineer - NodeJS</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEVME</t>
+          <t>Agiloft</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Git, MySQL, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=420d6f137457baed</t>
+          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer -Ford Pro Intelligence</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35bbcc66e3ba6ade</t>
+          <t>https://www.indeed.com/viewjob?jk=48384f9bd2f18aa4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software</t>
+          <t>Senior Site Reliability Engineer, Wikimedia Enterprise New</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Wikimedia Foundation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Terraform, Databricks, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, Kinesis, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be5ca184c7e91fe</t>
+          <t>https://www.indeed.com/viewjob?jk=38dbb3c218f7e9e1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Ads</t>
+          <t>Senior DevOps Engineer/Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>Stellar Cyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BigQuery, Docker, Kubernetes, BigQuery, Kafka, Python, R, Java, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, MongoDB, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2732d36e57a5b5</t>
+          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Quality Assurance Engineer and Tester</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>NimbleRx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Kubernetes, Jenkins, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, S3, Kinesis, CI/CD, Terraform, PySpark, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea8ee5a655912e8</t>
+          <t>https://www.indeed.com/viewjob?jk=143ac78ce4115c57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist, Supply Chain Simulation and Fulfillment</t>
+          <t>Data Scientist, Customer Experience</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2e20284ba542e2</t>
+          <t>https://www.indeed.com/viewjob?jk=76d23e05984ed87a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Data Scientist, Supply Chain Simulation and Fulfillment</t>
+          <t>Data Scientist, Customer Experience</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,42 +1161,847 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=270dbe2fe80568d8</t>
+          <t>https://www.indeed.com/viewjob?jk=dc91d791375a856d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Delivery (Remote)</t>
+          <t>Data Scientist, Customer Experience</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=137f26bf47a9a821</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Customer Experience</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Whatnot</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f1ded13c971e107</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Customer Experience</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Whatnot</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63184919e2d643e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Robots &amp; Pencils</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, S3, Redshift, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef2dc2586d8de903</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Java Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Copilot, Prompt Engineering, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a629a3b4a8f9184f</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer (contract)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Kubernetes, Jenkins, Git, Kafka, Hadoop, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d8ec8d04972fc0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Deep Learning Engineer II</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hayden AI</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=821054247d41b0bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Lovevery</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70ad7f6783d4ad61</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Robots &amp; Pencils</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Data Lake, Kinesis, CI/CD, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0485db6fd1a55330</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ketch</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, Cassandra, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=710a102d3715faa8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Databricks Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CoorsTek</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Golden, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CoStar Group</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, OpenCV, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2394171f0cde48f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Wiwynn International Corporation</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Socorro, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f26e06d78394ad0</t>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Tableau, Power BI, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d6f968546c0cdcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Application Developers</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Pasadena, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Git, MySQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b68bb3cc589bed26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, BigQuery, CI/CD, BigQuery, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2302d27093d4a475</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Data &amp; Insights, Surface &amp; HSE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edd994a71db0f30b</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Hadoop, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BusPatrol</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>S3, Docker, CI/CD, MySQL, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0f1133accccfb0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Network Engineer- WAN (Sr. Consultant level)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=269c1f46aab3ecbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Risk Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Lumin Digital</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbc638b06c3c4710</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EMERY SAPP &amp; SONS</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, BigQuery, CI/CD, BigQuery, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=998d4b8122790768</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Data Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Apache Airflow, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Optimal Inc.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=daa8938512c51e2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NLM Security Specialist I - III</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Lexical Intelligence, LLC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Hadoop, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c516f232221676d3</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-02.xlsx
+++ b/daily_matches/job_matches_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KLS Martin Group</t>
+          <t>The Emmes Company, LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, BigQuery, Synapse, Dataflow, Apache Airflow, Snowflake, BigQuery</t>
+          <t>Data Scientist, Generative AI, RAG, S3, Glue, Redshift, Kinesis, CI/CD, Git, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b464e799ea8089d</t>
+          <t>https://www.indeed.com/viewjob?jk=34ab205482e4b0a3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Back-End Software Engineer</t>
+          <t>AI Architect - Enterprise AI &amp; Generative AI Platforms - Multiple locations; Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quamputon</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,242 +531,242 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56492f350ebd9fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=77b44ab330bb3208</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fervo Energy</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Data Lake, FastAPI, Docker, CI/CD</t>
+          <t>LangChain, RAG, Pinecone, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e937b8d6d40093ff</t>
+          <t>https://www.indeed.com/viewjob?jk=2cac809c2033ba77</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist - Applied AI Scientist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, CI/CD, Git</t>
+          <t>RAG, Redshift, Synapse, Data Lake, CI/CD, Terraform, Snowflake, Databricks, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae80c1d7d907822</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7e3e5bab34cec5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NLM Bioinformatics Specialist and Developer (SME) I - III</t>
+          <t>Applied AI/ML Senior Associate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, PostgreSQL, MySQL</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762cbbd89d012daa</t>
+          <t>https://www.indeed.com/viewjob?jk=103af5ce571de29f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer - Marketing and Corporate Systems (ML Ops)</t>
+          <t>Applied Senior Software Engineer (AI Native Development)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, GCP Vertex AI, Azure ML, FastAPI, CI/CD</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering, CI/CD, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f849a29a849b37</t>
+          <t>https://www.indeed.com/viewjob?jk=c414b96260f8adaa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Solutions Architect (AI Native SDLC)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, BigQuery, Dataflow, AKS, CI/CD, Terraform</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0731089eba8c8af5</t>
+          <t>https://www.indeed.com/viewjob?jk=1a535d0166805777</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Applied AI/ML Senior Associate - Payments</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Neuroscale AI</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2671cfe0064b8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ded60e3f9faa93a4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NLM QA Specialist I - III</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,172 +776,172 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf4356318d88930</t>
+          <t>https://www.indeed.com/viewjob?jk=5afa70752c2ff290</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Software Engineer (Azure AI, Java/Angular Full-Stack)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Avnet</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, SQL</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42293692e8932ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=71e4e883bfa671e3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R</t>
+          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9537487871ae7</t>
+          <t>https://www.indeed.com/viewjob?jk=e05c14e44f4d784f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ca72623b1ecda0c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Gemini, BigQuery, CI/CD, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Python</t>
+          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
+          <t>https://www.indeed.com/viewjob?jk=b567dc076f197de9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Analyst, AI &amp; Analytics</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Agiloft</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>LangChain, RAG, Prompt Engineering, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
+          <t>https://www.indeed.com/viewjob?jk=c761542b4213e628</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer -Ford Pro Intelligence</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Bayview Asset Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,277 +986,277 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48384f9bd2f18aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=92db009b878de50d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Wikimedia Enterprise New</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wikimedia Foundation</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kinesis, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R</t>
+          <t>Generative AI, RAG, Git, Kafka, Hadoop, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dbb3c218f7e9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=8af0957fc860f6a7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer/Site Reliability Engineer</t>
+          <t>Engineer 1, Software Dev &amp; Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stellar Cyber</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, MongoDB, Python, R</t>
+          <t>RAG, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6323be947cc5653f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CCB Risk Modeling - AI ML Sr. Associate</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NimbleRx</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, CI/CD, Terraform, PySpark, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Git, Hadoop, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143ac78ce4115c57</t>
+          <t>https://www.indeed.com/viewjob?jk=9051530c297f21a8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist, Customer Experience</t>
+          <t>Software Development Engineer II - JavaScript Web Development</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>RAG, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d23e05984ed87a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba323d207ef1e2a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist, Customer Experience</t>
+          <t>Corporate- AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc91d791375a856d</t>
+          <t>https://www.indeed.com/viewjob?jk=28d5fe9cc2c0331b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist, Customer Experience</t>
+          <t>Senior Software Engineer - Medical Experience</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>RAG, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f26bf47a9a821</t>
+          <t>https://www.indeed.com/viewjob?jk=a7afa6ac6b5103ba</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist, Customer Experience</t>
+          <t>Senior Data Scientist — Applied Analytics (Data &amp; AI)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Kubernetes, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1ded13c971e107</t>
+          <t>https://www.indeed.com/viewjob?jk=105e05247bf56b5e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist, Customer Experience</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Nissan North America</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Smyrna, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>Data Scientist, Snowflake, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,742 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63184919e2d643e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Robots &amp; Pencils</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, S3, Redshift, Redshift, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2dc2586d8de903</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Java Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Charles Schwab</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Copilot, Prompt Engineering, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a629a3b4a8f9184f</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Kubernetes, Jenkins, Git, Kafka, Hadoop, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8ec8d04972fc0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Deep Learning Engineer II</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Hayden AI</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=821054247d41b0bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Lovevery</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70ad7f6783d4ad61</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Robots &amp; Pencils</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Data Lake, Kinesis, CI/CD, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0485db6fd1a55330</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Ketch</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, Cassandra, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=710a102d3715faa8</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Databricks Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>CoorsTek</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Golden, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>CoStar Group</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, OpenCV, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2394171f0cde48f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AI Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Wiwynn International Corporation</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Socorro, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Tableau, Power BI, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6f968546c0cdcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Application Developers</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ADP</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Pasadena, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Jenkins, Git, MySQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b68bb3cc589bed26</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior AI Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Columbia, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, BigQuery, CI/CD, BigQuery, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2302d27093d4a475</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Data &amp; Insights, Surface &amp; HSE</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Chevron</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edd994a71db0f30b</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Epsilon</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Hadoop, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>BusPatrol</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>S3, Docker, CI/CD, MySQL, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f1133accccfb0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Network Engineer- WAN (Sr. Consultant level)</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=269c1f46aab3ecbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Risk Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Lumin Digital</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbc638b06c3c4710</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior AI Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>EMERY SAPP &amp; SONS</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Columbia, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, BigQuery, CI/CD, BigQuery, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=998d4b8122790768</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior Data Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Apache Airflow, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Agentic AI Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Optimal Inc.</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=daa8938512c51e2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>NLM Security Specialist I - III</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Lexical Intelligence, LLC</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Data Scientist, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Hadoop, R</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c516f232221676d3</t>
+          <t>https://www.indeed.com/viewjob?jk=056b0145bbe6c0f1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-02.xlsx
+++ b/daily_matches/job_matches_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Emmes Company, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, S3, Glue, Redshift, Kinesis, CI/CD, Git, Redshift</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ab205482e4b0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9be0e32027026424</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Architect - Enterprise AI &amp; Generative AI Platforms - Multiple locations; Remote</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b44ab330bb3208</t>
+          <t>https://www.indeed.com/viewjob?jk=e68993f91fa3f1b4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cac809c2033ba77</t>
+          <t>https://www.indeed.com/viewjob?jk=628201dada39104f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Synapse, Data Lake, CI/CD, Terraform, Snowflake, Databricks, Redshift, PySpark</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7e3e5bab34cec5</t>
+          <t>https://www.indeed.com/viewjob?jk=17ee918f557dad60</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Applied AI/ML Senior Associate</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks, PySpark</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103af5ce571de29f</t>
+          <t>https://www.indeed.com/viewjob?jk=d89f724d90d39f1a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applied Senior Software Engineer (AI Native Development)</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering, CI/CD, Git</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c414b96260f8adaa</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb73281d17dd7f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solutions Architect (AI Native SDLC)</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering, CI/CD</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a535d0166805777</t>
+          <t>https://www.indeed.com/viewjob?jk=928d83034a8588c4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Applied AI/ML Senior Associate - Payments</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks, PySpark, Python</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded60e3f9faa93a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e19e44b8ef2cbfc7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afa70752c2ff290</t>
+          <t>https://www.indeed.com/viewjob?jk=bd91d3d4221ab6c8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e4e883bfa671e3</t>
+          <t>https://www.indeed.com/viewjob?jk=709cd6837bc31b47</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e05c14e44f4d784f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf62483ea94871fc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ca72623b1ecda0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ad3b9ffbf1a1c5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,102 +916,102 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b567dc076f197de9</t>
+          <t>https://www.indeed.com/viewjob?jk=27464971a8de0b62</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analyst, AI &amp; Analytics</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c761542b4213e628</t>
+          <t>https://www.indeed.com/viewjob?jk=ac11b38d058e456a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bayview Asset Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92db009b878de50d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c427842476a9845</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Git, Kafka, Hadoop, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af0957fc860f6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e590e631ed3731a1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer 1, Software Dev &amp; Engineering</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6323be947cc5653f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9680315af02331</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CCB Risk Modeling - AI ML Sr. Associate</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Git, Hadoop, Python, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9051530c297f21a8</t>
+          <t>https://www.indeed.com/viewjob?jk=770c38ee65bb6062</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - JavaScript Web Development</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba323d207ef1e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a328d7361f15199</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Corporate- AI Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Python, SQL, R, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d5fe9cc2c0331b</t>
+          <t>https://www.indeed.com/viewjob?jk=9e159100e52ecbaf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Medical Experience</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7afa6ac6b5103ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d97f8b67ac923201</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Scientist — Applied Analytics (Data &amp; AI)</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Kubernetes, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,42 +1231,2877 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105e05247bf56b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=c55ec597154d2272</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nissan North America</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Smyrna, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb331ccb94124f99</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2cec2ae3282a2e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fcd73d5c5e6202f</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=586c88459fbb0f45</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e48010dc3a1202d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2337d6b23ef3e27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ced6f7a33f86e685</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18f275e19ded062a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8708de56a7f54bb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3959e4229ad7ab7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=144e16ada1b5a9ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8571d804c3e2af21</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15445b689370c772</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e63010208c6e8b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e79ecfc2a85326ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70bd54ff64ef9514</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f22be107213655b</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c3954b773cda740</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7520782451b1ea33</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a16389d2443deac</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff8f530a20b3705d</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42d5bf7d1da35b7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fbcbf5c35629fe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ec57015b662f733</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0e4be7e924b1ce2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3117cbef0400ac1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75220828d5bebb59</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57688f9ac8e58277</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fff3ba0293d267a</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI Platform Architect (contract)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Pinecone, Prompt Engineering, S3, Glue, Athena, Redshift, Data Lake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4035741c18917073</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DevOps/Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Baanyan Software Services, Inc</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccf9f4c45dab8812</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Product Software Engineer - Ad Platform (Audience Team)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, Kubernetes, CI/CD, Terraform, Kafka, MySQL, Cassandra, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06f108b3fa1b3553</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist I - (AI Focus)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Principal Financial Group</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Keras, AWS SageMaker, Git, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81bf63d92d5e87ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Site Reliability / Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>General Intuition &amp; Medal</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, MySQL, SQL</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=235e8563d0407abd</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Site Reliability / Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Medal</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, MySQL, SQL</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dd6b80058693cb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AppCast</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Athena, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2334de1166b895fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=853f304c4fea8ef7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=855d996d6f780ae7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0dfce6c1d4ad55a</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=777bd37e520ab857</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76da643450ea8ff1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=367f57f5d7c46512</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70958ae9c65a14af</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ca4d042a90c3371</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34833a6b6b34b0bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8a3699e30c2caf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2694b298c133118</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31a495d44eb4372b</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AI Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Hayden Industrial</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, FastAPI, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b539cf2fd5d25c44</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AI/ML SOFTWARE ENGINEER</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Peraton</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Basking Ridge, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cccd80c91813f5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SOFTWARE ENGINEER - AGENTIC AI PLATFORM</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Peraton</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Basking Ridge, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=371fb36697bb3cfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Data Lake, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbda51fe27c52909</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Vizient, Inc.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6414c2329a6a918</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Full Stack Applications Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Adarga</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, MySQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=504911ab6aa849e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Automation Engineer, Agentic Orchestration</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>StackAdapt</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, TensorFlow, PyTorch, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe1cc5e5ac45fe22</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b05e070c05e88960</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f52e450df00126ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32220fd756f87c97</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=737b20cb42e32e16</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6fb09956ff97673</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Arlington Heights, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=483d4062cba7e1fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca9912dbd04229ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0bdd3bd692cb6b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afa2d5195e9bb1b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13a90f357fde7702</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77410f313db981f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a6f151df05ac27e</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5963bf07707031e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect, Gen AI</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Git, R</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e11b00a9b4873c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Infosmart Technologies Inc</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Cupertino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
         <v>10</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, Snowflake, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Pinecone, Docker, Kubernetes, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad17ea5ed422c71c</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Professional, Software Engineer - AI</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MVP Health Care</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Schenectady, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff6ae000de6f5fb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Valley Bank</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3aaec8e40a2838c</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer or Intern</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Advanced Materials and Devices</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Reno, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>S3, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eff27030d7d9bc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a86b710898e7f77</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Trenton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b099ceaaffdbf0cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e5ee6c1dab5a95d</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Springfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e23f486f56d19ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Dover, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=086ffa9dc2133ac4</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3246bad92ad7a41</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df7141c192a2abaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eed603d5cd3fab62</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=056b0145bbe6c0f1</t>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4922d62500eb2667</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-02.xlsx
+++ b/daily_matches/job_matches_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be0e32027026424</t>
+          <t>https://www.indeed.com/viewjob?jk=bd8ed8c31995022e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e68993f91fa3f1b4</t>
+          <t>https://www.indeed.com/viewjob?jk=36a6189225b69d8e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628201dada39104f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d547c4276a9dd4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17ee918f557dad60</t>
+          <t>https://www.indeed.com/viewjob?jk=dce8b82e84b86638</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89f724d90d39f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=56be7f03b4d07422</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb73281d17dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=329212424ae72e0b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928d83034a8588c4</t>
+          <t>https://www.indeed.com/viewjob?jk=23816024d11c09d8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e19e44b8ef2cbfc7</t>
+          <t>https://www.indeed.com/viewjob?jk=aebc369e1dedd710</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd91d3d4221ab6c8</t>
+          <t>https://www.indeed.com/viewjob?jk=24968a01dadf331a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709cd6837bc31b47</t>
+          <t>https://www.indeed.com/viewjob?jk=02e5a998bb23e2b8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf62483ea94871fc</t>
+          <t>https://www.indeed.com/viewjob?jk=61f4316554d846d8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ad3b9ffbf1a1c5</t>
+          <t>https://www.indeed.com/viewjob?jk=41185be64561580d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27464971a8de0b62</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5faf525ce5066c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac11b38d058e456a</t>
+          <t>https://www.indeed.com/viewjob?jk=a868fb9222a17f31</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c427842476a9845</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e76b1a8bd7d23b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e590e631ed3731a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6b0d07da6ac2093</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Engineer - API Platform Engineer - CDH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9680315af02331</t>
+          <t>https://www.indeed.com/viewjob?jk=d846903d81c33e82</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Full Stack and AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Pinecone, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=770c38ee65bb6062</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f94b5acff92730</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a328d7361f15199</t>
+          <t>https://www.indeed.com/viewjob?jk=4a585d9e5f8d2b5e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e159100e52ecbaf</t>
+          <t>https://www.indeed.com/viewjob?jk=25b51410dd8ffd88</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97f8b67ac923201</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fed518d6fe919b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Engineering Intern, Agentic Systems</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Atlas Travel &amp; Technology Group, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, RAG, LLaMA, Copilot, Pinecone, BigQuery, FastAPI, CI/CD, Git, BigQuery</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55ec597154d2272</t>
+          <t>https://www.indeed.com/viewjob?jk=bea3b268de79ef6e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Sr. SW Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>LangChain, RAG, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb331ccb94124f99</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34ffc2395f400e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Media DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2cec2ae3282a2e6</t>
+          <t>https://www.indeed.com/viewjob?jk=568eedaf2dddb4e6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Generative AI, RAG, Copilot, BigQuery, Data Lake, Dataflow, BigQuery, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fcd73d5c5e6202f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ca03311ac42217</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586c88459fbb0f45</t>
+          <t>https://www.indeed.com/viewjob?jk=d05d8b56b72079c9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Computer Vision Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Matrix Design Group, LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Newburgh, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, LLaMA, Pinecone, TensorFlow, PyTorch, YOLO, Azure ML, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48010dc3a1202d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b81f6275f5bb737</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Sr AI Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, Pinecone, FastAPI, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2337d6b23ef3e27</t>
+          <t>https://www.indeed.com/viewjob?jk=8e01343345f387b3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer - SRE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced6f7a33f86e685</t>
+          <t>https://www.indeed.com/viewjob?jk=c48d396577280e6f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f275e19ded062a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9faea0d55a841c9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8708de56a7f54bb9</t>
+          <t>https://www.indeed.com/viewjob?jk=2abbc5f73ae2028d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3959e4229ad7ab7b</t>
+          <t>https://www.indeed.com/viewjob?jk=33de66454718a7f8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=144e16ada1b5a9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f96d64f561456df6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8571d804c3e2af21</t>
+          <t>https://www.indeed.com/viewjob?jk=d05047e3838d26d9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Sr. DevOps Engineer - AI and Site Reliability Engineering</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Generative AI, RAG, TensorFlow, AWS SageMaker, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15445b689370c772</t>
+          <t>https://www.indeed.com/viewjob?jk=7c13ae1d1f995cbf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Interra Credit Union</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Goshen, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, BigQuery, Data Lake, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e63010208c6e8b0</t>
+          <t>https://www.indeed.com/viewjob?jk=4221f001ea95bed0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ReadyOn</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Data Scientist, RAG, Glue, Apache Airflow, Snowflake, PySpark, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ecfc2a85326ce</t>
+          <t>https://www.indeed.com/viewjob?jk=15705014fe84a21e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer III (6193)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Generative AI, RAG, Copilot, FAISS, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70bd54ff64ef9514</t>
+          <t>https://www.indeed.com/viewjob?jk=76d676f5bf647822</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22be107213655b</t>
+          <t>https://www.indeed.com/viewjob?jk=71154672a5c4c774</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3954b773cda740</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf9837fea6d0016</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7520782451b1ea33</t>
+          <t>https://www.indeed.com/viewjob?jk=32094da9dbd2d3c3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a16389d2443deac</t>
+          <t>https://www.indeed.com/viewjob?jk=aab81f237ba129b0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Web Front-End Developer – Agentic AI Applications</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, R, Java</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff8f530a20b3705d</t>
+          <t>https://www.indeed.com/viewjob?jk=6932eac5c8127278</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Scientist - Innovation - PhD (Irving, TX)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, RAG, PyTorch, S3, EC2, MLflow, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42d5bf7d1da35b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=306cc72d88b6d4d7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>State of Wisconsin Investment Board</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Data Scientist, RAG, CI/CD, Terraform, Git, Snowflake, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fbcbf5c35629fe8</t>
+          <t>https://www.indeed.com/viewjob?jk=124c410c8db6510c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, RAG, Cortex, Apache Airflow, CI/CD, Git, Snowflake, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ec57015b662f733</t>
+          <t>https://www.indeed.com/viewjob?jk=b81577b0577b88ad</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Systems Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, AWS SageMaker, CI/CD, Databricks, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e4be7e924b1ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=2d81636c6428aa52</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer, AI Platform &amp; Agents</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Coalition Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Docker, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3117cbef0400ac1d</t>
+          <t>https://www.indeed.com/viewjob?jk=28a92761cc510188</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75220828d5bebb59</t>
+          <t>https://www.indeed.com/viewjob?jk=3299f19f42a9fa4d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Sr. Measurement Scientist, Solution Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, SQL, R, Bayesian</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57688f9ac8e58277</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9a056f8c78d253</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Pulse GenAI Engineering build Sr Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fff3ba0293d267a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0de47a4e7211abf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Platform Architect (contract)</t>
+          <t>Back-end Software Engineer - Seattle, WA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Otter</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>17.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Pinecone, Prompt Engineering, S3, Glue, Athena, Redshift, Data Lake, CI/CD</t>
+          <t>Docker, Kubernetes, Git, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4035741c18917073</t>
+          <t>https://www.indeed.com/viewjob?jk=c03b7513e17f08df</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps/Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Baanyan Software Services, Inc</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccf9f4c45dab8812</t>
+          <t>https://www.indeed.com/viewjob?jk=7c4f516403858ed9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer - Ad Platform (Audience Team)</t>
+          <t>Intern, Software Engineering - Data Science Engineering (Broomfield, CO)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, Kubernetes, CI/CD, Terraform, Kafka, MySQL, Cassandra, NoSQL, Python</t>
+          <t>Data Scientist, RAG, Docker, Jenkins, Snowflake, Databricks, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f108b3fa1b3553</t>
+          <t>https://www.indeed.com/viewjob?jk=3522fa6dac777c5c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Data Scientist I - (AI Focus)</t>
+          <t>Associate Cloud AI Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Principal Financial Group</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2372,186 +2372,186 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Keras, AWS SageMaker, Git, Snowflake, Databricks, Python</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81bf63d92d5e87ed</t>
+          <t>https://www.indeed.com/viewjob?jk=41410c8c92de1692</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>TriNet</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, MySQL, SQL</t>
+          <t>Generative AI, RAG, Copilot, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235e8563d0407abd</t>
+          <t>https://www.indeed.com/viewjob?jk=bf56796857b1e7d2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>TriNet</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, MySQL, SQL</t>
+          <t>Generative AI, RAG, Copilot, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd6b80058693cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8157139b6eb5d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AppCast</t>
+          <t>TriNet</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Athena, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2334de1166b895fb</t>
+          <t>https://www.indeed.com/viewjob?jk=06624481a2180b0c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TriNet</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>Generative AI, RAG, Copilot, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853f304c4fea8ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca919787780a3d8e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Delaware Electric Cooperative</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Greenwood, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>Data Scientist, TensorFlow, Power BI, Python, SQL, R, Java, Julia, Scala, Optimization</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=855d996d6f780ae7</t>
+          <t>https://www.indeed.com/viewjob?jk=c06b494533be2687</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Data Scientist/Data Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>vectorsoft</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0dfce6c1d4ad55a</t>
+          <t>https://www.indeed.com/viewjob?jk=cff4161560790df7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Engineer, Digital Products</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NDWA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>RAG, Prompt Engineering, S3, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777bd37e520ab857</t>
+          <t>https://www.indeed.com/viewjob?jk=807809781a081dc7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior API Engineer - Advisor I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>RAG, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76da643450ea8ff1</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c5308e0ee7b406</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior GenAI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Niskayuna, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, PyTorch, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=367f57f5d7c46512</t>
+          <t>https://www.indeed.com/viewjob?jk=bb290685fe55adf9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>Data Scientist, Generative AI, PyTorch, CI/CD, Git, PySpark, Python, R, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70958ae9c65a14af</t>
+          <t>https://www.indeed.com/viewjob?jk=16b0613813de30cc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Software Engineer-Configuration &amp; Build Engineering</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Source Code Technology</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ca4d042a90c3371</t>
+          <t>https://www.indeed.com/viewjob?jk=10edbb7e97481fb9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, R, Java, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34833a6b6b34b0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=3e25613edb19949d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>.Net Fullstack Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>S3, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a3699e30c2caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=0d011c6ed693c14f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Argo Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2694b298c133118</t>
+          <t>https://www.indeed.com/viewjob?jk=fee3cdec10b4f2b4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Postdoctoral Appointee - AI for Biomedical Discovery</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a495d44eb4372b</t>
+          <t>https://www.indeed.com/viewjob?jk=50e99602082cb5b6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Senior Software Engineer – (C#/.NET &amp; SQL -Required)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hayden Industrial</t>
+          <t>Index AR Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Williamsburg, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, FastAPI, Docker, Git, Python</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b539cf2fd5d25c44</t>
+          <t>https://www.indeed.com/viewjob?jk=669d6eeda04270d5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI/ML SOFTWARE ENGINEER</t>
+          <t>Summer 2026 Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Boston Public Health Commission</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, PostgreSQL, Python</t>
+          <t>Data Lake, GitHub Actions, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,102 +2981,102 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cccd80c91813f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=808a21fcdc4b6706</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER - AGENTIC AI PLATFORM</t>
+          <t>Full Stack Engineering Specialist - Freelance AI Trainer Project</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Meridial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, PostgreSQL, Python</t>
+          <t>Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371fb36697bb3cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=57c804bbb73ffe82</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineering Specialist - Freelance AI Trainer Project</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Meridial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbda51fe27c52909</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1fd440437fd44</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Home Loans Loss Forecasting Analytics, Senior Data Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R</t>
+          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6414c2329a6a918</t>
+          <t>https://www.indeed.com/viewjob?jk=cc044148f10ae5f7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Applications Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Adarga</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Docker, Kubernetes, MySQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,987 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=504911ab6aa849e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Automation Engineer, Agentic Orchestration</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>StackAdapt</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, TensorFlow, PyTorch, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1cc5e5ac45fe22</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e070c05e88960</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f52e450df00126ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32220fd756f87c97</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=737b20cb42e32e16</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6fb09956ff97673</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Arlington Heights, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=483d4062cba7e1fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Westlake, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9912dbd04229ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bdd3bd692cb6b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afa2d5195e9bb1b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13a90f357fde7702</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77410f313db981f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a6f151df05ac27e</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5963bf07707031e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Solutions Architect, Gen AI</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Git, R</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e11b00a9b4873c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>AI / ML Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Infosmart Technologies Inc</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Cupertino, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Docker, Kubernetes, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad17ea5ed422c71c</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Professional, Software Engineer - AI</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>MVP Health Care</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Schenectady, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6ae000de6f5fb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Valley Bank</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3aaec8e40a2838c</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer or Intern</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Advanced Materials and Devices</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Reno, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>S3, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7eff27030d7d9bc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7a86b710898e7f77</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Trenton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b099ceaaffdbf0cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5ee6c1dab5a95d</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Springfield, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23f486f56d19ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Dover, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=086ffa9dc2133ac4</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3246bad92ad7a41</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df7141c192a2abaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Albany, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eed603d5cd3fab62</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI/ML &amp; Agentic)</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4922d62500eb2667</t>
+          <t>https://www.indeed.com/viewjob?jk=a450ef533eba017b</t>
         </is>
       </c>
     </row>
